--- a/data/trans_bre/IP1020-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,1</t>
+          <t>-5,88; 1,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 7,03</t>
+          <t>-3,57; 7,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,67</t>
+          <t>-3,16; 1,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 0,0</t>
+          <t>-5,98; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-85,1; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,33</t>
+          <t>-3,06; 1,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,21</t>
+          <t>-0,76; 4,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,26</t>
+          <t>-3,29; 4,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 4,66</t>
+          <t>-4,64; 4,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,19 +790,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,75; 336,18</t>
+          <t>-70,77; 419,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,41; 269,98</t>
+          <t>-82,65; 270,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 14,09</t>
+          <t>2,34; 13,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,0</t>
+          <t>-5,67; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,98</t>
+          <t>-7,69; 2,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 180,18</t>
+          <t>-100,0; 242,72</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,0</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 5,38</t>
+          <t>-2,88; 4,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,77</t>
+          <t>-5,42; 1,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,44</t>
+          <t>1,31; 14,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 5,07</t>
+          <t>-3,08; 5,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,19</t>
+          <t>-5,75; 5,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,04</t>
+          <t>-2,08; 4,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 4,46</t>
+          <t>-8,27; 4,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 0,0</t>
+          <t>-7,44; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,42</t>
+          <t>-5,65; 5,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 386,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,72</t>
+          <t>-0,96; 1,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,48</t>
+          <t>0,07; 4,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,17</t>
+          <t>-1,42; 2,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,34</t>
+          <t>-5,13; 5,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-59,4; 107,1</t>
+          <t>-57,89; 130,36</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,44</t>
+          <t>-1,72; 2,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,71</t>
+          <t>-1,86; 0,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,17</t>
+          <t>-3,77; 1,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 3,01</t>
+          <t>-2,78; 2,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 194,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,78</t>
+          <t>-0,92; 0,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,48</t>
+          <t>-0,04; 2,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,6</t>
+          <t>-1,62; 0,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,88</t>
+          <t>-1,46; 1,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-72,25; 158,21</t>
+          <t>-72,36; 143,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 292,55</t>
+          <t>-10,34; 274,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 61,85</t>
+          <t>-65,28; 51,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 76,63</t>
+          <t>-37,27; 70,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 1,14</t>
+          <t>-5,88; 2,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 7,86</t>
+          <t>-3,6; 8,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,67</t>
+          <t>-3,47; 1,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 0,0</t>
+          <t>-5,17; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,1; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,37</t>
+          <t>-2,51; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,16</t>
+          <t>-0,83; 4,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 4,53</t>
+          <t>-3,67; 4,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 4,34</t>
+          <t>-4,51; 4,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,77; 419,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,65; 270,0</t>
+          <t>-82,16; 330,57</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 13,8</t>
+          <t>2,22; 14,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 0,0</t>
+          <t>-4,46; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 2,71</t>
+          <t>-8,44; 2,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 242,72</t>
+          <t>-100,0; 154,22</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>-3,69; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 4,95</t>
+          <t>-2,9; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,65</t>
+          <t>-6,13; 1,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,13</t>
+          <t>1,31; 11,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 5,16</t>
+          <t>-3,07; 5,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 8,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 5,89</t>
+          <t>-5,75; 6,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,1</t>
+          <t>-2,09; 4,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 4,34</t>
+          <t>-8,47; 4,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,0</t>
+          <t>-6,36; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 5,18</t>
+          <t>-4,89; 4,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 386,34</t>
+          <t>-100,0; 474,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,82</t>
+          <t>-0,96; 1,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,59</t>
+          <t>0,09; 4,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,23</t>
+          <t>-1,79; 1,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 5,2</t>
+          <t>-5,47; 4,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,89; 130,36</t>
+          <t>-61,15; 104,12</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,17</t>
+          <t>-1,54; 2,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,71</t>
+          <t>-1,89; 0,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,02</t>
+          <t>-3,46; 1,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,95</t>
+          <t>-2,59; 3,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 203,28</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,66</t>
+          <t>-0,81; 0,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,44</t>
+          <t>-0,04; 2,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,57</t>
+          <t>-1,44; 0,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,79</t>
+          <t>-1,59; 1,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-72,36; 143,0</t>
+          <t>-70,82; 135,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 274,72</t>
+          <t>-8,61; 260,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 51,53</t>
+          <t>-63,25; 55,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 70,28</t>
+          <t>-41,21; 67,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,19</t>
+          <t>-5,92; 2,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 8,64</t>
+          <t>-4,52; 7,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,65</t>
+          <t>-4,0; 1,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,0</t>
+          <t>-5,12; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,35</t>
+          <t>-3,07; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,25</t>
+          <t>-0,6; 4,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 4,3</t>
+          <t>-3,45; 4,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,46</t>
+          <t>-3,26; 5,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,75; 336,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,16; 330,57</t>
+          <t>-70,32; 379,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-44,2%</t>
+          <t>-46,91%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 14,81</t>
+          <t>2,4; 14,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,0</t>
+          <t>-5,56; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 2,7</t>
+          <t>-8,15; 2,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,22</t>
+          <t>-100,0; 170,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,0</t>
+          <t>-3,37; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 5,46</t>
+          <t>-2,87; 5,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 1,86</t>
+          <t>-6,23; 1,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,88</t>
+          <t>1,51; 14,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,28</t>
+          <t>-3,05; 5,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,59</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 6,33</t>
+          <t>-5,12; 6,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-13,97%</t>
+          <t>-4,92%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,82</t>
+          <t>-2,09; 4,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 4,2</t>
+          <t>-8,52; 4,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,0</t>
+          <t>-7,72; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 4,57</t>
+          <t>-5,35; 4,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 474,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-6,77%</t>
+          <t>-14,03%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,71</t>
+          <t>-0,96; 1,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,59</t>
+          <t>0,29; 5,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,91</t>
+          <t>-1,82; 2,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 4,48</t>
+          <t>-6,45; 4,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 104,12</t>
+          <t>-62,13; 91,03</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,26</t>
+          <t>-1,46; 2,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,37</t>
+          <t>-1,87; 0,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,15</t>
+          <t>-3,67; 1,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,07</t>
+          <t>-3,03; 2,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 203,28</t>
+          <t>-100,0; 194,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,69</t>
+          <t>-0,89; 0,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,55</t>
+          <t>0,1; 2,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,65</t>
+          <t>-1,34; 0,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,84</t>
+          <t>-1,34; 2,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-70,82; 135,01</t>
+          <t>-72,25; 158,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 260,56</t>
+          <t>2,58; 292,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 55,88</t>
+          <t>-62,44; 61,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 67,9</t>
+          <t>-33,66; 82,75</t>
         </is>
       </c>
     </row>
